--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4473-2025 artfynd.xlsx
+++ b/artfynd/A 4473-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322910</v>
       </c>
       <c r="B2" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
